--- a/artfynd/A 4552-2022 artfynd.xlsx
+++ b/artfynd/A 4552-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105166887</v>
+        <v>105166886</v>
       </c>
       <c r="B2" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600576.9869002764</v>
+        <v>600660</v>
       </c>
       <c r="R2" t="n">
-        <v>7038326.47402689</v>
+        <v>7038355</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-09-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,19 +776,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105166937</v>
+        <v>105166888</v>
       </c>
       <c r="B3" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600430.5413504761</v>
+        <v>600431</v>
       </c>
       <c r="R3" t="n">
-        <v>7038209.528958893</v>
+        <v>7038210</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2022-09-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105166886</v>
+        <v>105166890</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600659.9015348073</v>
+        <v>600400</v>
       </c>
       <c r="R4" t="n">
-        <v>7038354.597671548</v>
+        <v>7038144</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2022-09-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105166938</v>
+        <v>105166887</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600527.8089762112</v>
+        <v>600577</v>
       </c>
       <c r="R5" t="n">
-        <v>7038265.849388626</v>
+        <v>7038327</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2022-09-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,16 +1082,11 @@
         <v>105166885</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600645.7588016914</v>
+        <v>600646</v>
       </c>
       <c r="R6" t="n">
-        <v>7038348.333687993</v>
+        <v>7038349</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2022-09-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,6 +1173,107 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>105166889</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>600528</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7038266</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>

--- a/artfynd/A 4552-2022 artfynd.xlsx
+++ b/artfynd/A 4552-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166886</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166888</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166890</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166887</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166885</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,8 +1308,21 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166889</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>